--- a/artfynd/A 49447-2022 artfynd.xlsx
+++ b/artfynd/A 49447-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122546336</v>
       </c>
       <c r="B2" t="n">
-        <v>91502</v>
+        <v>91515</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122546233</v>
+        <v>122546276</v>
       </c>
       <c r="B3" t="n">
-        <v>92079</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,16 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772560</v>
+        <v>772628</v>
       </c>
       <c r="R3" t="n">
-        <v>7113275</v>
+        <v>7113321</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +886,7 @@
         <v>122546163</v>
       </c>
       <c r="B4" t="n">
-        <v>90813</v>
+        <v>90826</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,6 +900,11 @@
       </c>
       <c r="E4" t="n">
         <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -979,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122546276</v>
+        <v>122546233</v>
       </c>
       <c r="B5" t="n">
-        <v>78652</v>
+        <v>92092</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -995,16 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4361</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1014,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>772628</v>
+        <v>772560</v>
       </c>
       <c r="R5" t="n">
-        <v>7113321</v>
+        <v>7113275</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 49447-2022 artfynd.xlsx
+++ b/artfynd/A 49447-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122546336</v>
       </c>
       <c r="B2" t="n">
-        <v>91515</v>
+        <v>91528</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122546163</v>
+        <v>122546233</v>
       </c>
       <c r="B4" t="n">
-        <v>90826</v>
+        <v>92105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>772567</v>
+        <v>772560</v>
       </c>
       <c r="R4" t="n">
-        <v>7113274</v>
+        <v>7113275</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122546233</v>
+        <v>122546163</v>
       </c>
       <c r="B5" t="n">
-        <v>92092</v>
+        <v>90839</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,21 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>772560</v>
+        <v>772567</v>
       </c>
       <c r="R5" t="n">
-        <v>7113275</v>
+        <v>7113274</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 49447-2022 artfynd.xlsx
+++ b/artfynd/A 49447-2022 artfynd.xlsx
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122546233</v>
+        <v>122546163</v>
       </c>
       <c r="B4" t="n">
-        <v>92105</v>
+        <v>90839</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>772560</v>
+        <v>772567</v>
       </c>
       <c r="R4" t="n">
-        <v>7113275</v>
+        <v>7113274</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122546163</v>
+        <v>122546233</v>
       </c>
       <c r="B5" t="n">
-        <v>90839</v>
+        <v>92105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,21 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>772567</v>
+        <v>772560</v>
       </c>
       <c r="R5" t="n">
-        <v>7113274</v>
+        <v>7113275</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 49447-2022 artfynd.xlsx
+++ b/artfynd/A 49447-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122546336</v>
+        <v>122546163</v>
       </c>
       <c r="B2" t="n">
-        <v>91528</v>
+        <v>90833</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>757</v>
+        <v>1202</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772541</v>
+        <v>772567</v>
       </c>
       <c r="R2" t="n">
-        <v>7113281</v>
+        <v>7113274</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122546276</v>
+        <v>122546336</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>91529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +797,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772628</v>
+        <v>772541</v>
       </c>
       <c r="R3" t="n">
-        <v>7113321</v>
+        <v>7113281</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,6 +860,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122546163</v>
+        <v>122546276</v>
       </c>
       <c r="B4" t="n">
-        <v>90839</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>772567</v>
+        <v>772628</v>
       </c>
       <c r="R4" t="n">
-        <v>7113274</v>
+        <v>7113321</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +992,7 @@
         <v>122546233</v>
       </c>
       <c r="B5" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 49447-2022 artfynd.xlsx
+++ b/artfynd/A 49447-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122546163</v>
+        <v>122546276</v>
       </c>
       <c r="B2" t="n">
-        <v>90833</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772567</v>
+        <v>772628</v>
       </c>
       <c r="R2" t="n">
-        <v>7113274</v>
+        <v>7113321</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122546336</v>
+        <v>122546233</v>
       </c>
       <c r="B3" t="n">
-        <v>91529</v>
+        <v>92106</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,16 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>757</v>
+        <v>4361</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772541</v>
+        <v>772560</v>
       </c>
       <c r="R3" t="n">
-        <v>7113281</v>
+        <v>7113275</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +865,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -883,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122546276</v>
+        <v>122546336</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>91529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,21 +903,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>772628</v>
+        <v>772541</v>
       </c>
       <c r="R4" t="n">
-        <v>7113321</v>
+        <v>7113281</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,6 +966,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122546233</v>
+        <v>122546163</v>
       </c>
       <c r="B5" t="n">
-        <v>92106</v>
+        <v>90833</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,21 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>772560</v>
+        <v>772567</v>
       </c>
       <c r="R5" t="n">
-        <v>7113275</v>
+        <v>7113274</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 49447-2022 artfynd.xlsx
+++ b/artfynd/A 49447-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122546276</v>
+        <v>122546336</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>91530</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772628</v>
+        <v>772541</v>
       </c>
       <c r="R2" t="n">
-        <v>7113321</v>
+        <v>7113281</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +754,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122546233</v>
+        <v>122546276</v>
       </c>
       <c r="B3" t="n">
-        <v>92106</v>
+        <v>78657</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772560</v>
+        <v>772628</v>
       </c>
       <c r="R3" t="n">
-        <v>7113275</v>
+        <v>7113321</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122546336</v>
+        <v>122546163</v>
       </c>
       <c r="B4" t="n">
-        <v>91529</v>
+        <v>90834</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,16 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>757</v>
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>772541</v>
+        <v>772567</v>
       </c>
       <c r="R4" t="n">
-        <v>7113281</v>
+        <v>7113274</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +967,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122546163</v>
+        <v>122546233</v>
       </c>
       <c r="B5" t="n">
-        <v>90833</v>
+        <v>92107</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,21 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>772567</v>
+        <v>772560</v>
       </c>
       <c r="R5" t="n">
-        <v>7113274</v>
+        <v>7113275</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 49447-2022 artfynd.xlsx
+++ b/artfynd/A 49447-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122546336</v>
       </c>
       <c r="B2" t="n">
-        <v>91530</v>
+        <v>91533</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>122546276</v>
       </c>
       <c r="B3" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122546163</v>
+        <v>122546233</v>
       </c>
       <c r="B4" t="n">
-        <v>90834</v>
+        <v>92110</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>772567</v>
+        <v>772560</v>
       </c>
       <c r="R4" t="n">
-        <v>7113274</v>
+        <v>7113275</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122546233</v>
+        <v>122546163</v>
       </c>
       <c r="B5" t="n">
-        <v>92107</v>
+        <v>90837</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,21 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>772560</v>
+        <v>772567</v>
       </c>
       <c r="R5" t="n">
-        <v>7113275</v>
+        <v>7113274</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 49447-2022 artfynd.xlsx
+++ b/artfynd/A 49447-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122546336</v>
+        <v>122546233</v>
       </c>
       <c r="B2" t="n">
-        <v>91533</v>
+        <v>92110</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>757</v>
+        <v>4361</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772541</v>
+        <v>772560</v>
       </c>
       <c r="R2" t="n">
-        <v>7113281</v>
+        <v>7113275</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122546276</v>
+        <v>122546163</v>
       </c>
       <c r="B3" t="n">
-        <v>78660</v>
+        <v>90837</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772628</v>
+        <v>772567</v>
       </c>
       <c r="R3" t="n">
-        <v>7113321</v>
+        <v>7113274</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122546233</v>
+        <v>122546336</v>
       </c>
       <c r="B4" t="n">
-        <v>92110</v>
+        <v>91533</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,21 +903,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Orange taggsvamp</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>772560</v>
+        <v>772541</v>
       </c>
       <c r="R4" t="n">
-        <v>7113275</v>
+        <v>7113281</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,6 +966,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122546163</v>
+        <v>122546276</v>
       </c>
       <c r="B5" t="n">
-        <v>90837</v>
+        <v>78660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,21 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>772567</v>
+        <v>772628</v>
       </c>
       <c r="R5" t="n">
-        <v>7113274</v>
+        <v>7113321</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 49447-2022 artfynd.xlsx
+++ b/artfynd/A 49447-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122546233</v>
+        <v>122546336</v>
       </c>
       <c r="B2" t="n">
-        <v>92110</v>
+        <v>91636</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Orange taggsvamp</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772560</v>
+        <v>772541</v>
       </c>
       <c r="R2" t="n">
-        <v>7113275</v>
+        <v>7113281</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +754,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122546163</v>
+        <v>122546276</v>
       </c>
       <c r="B3" t="n">
-        <v>90837</v>
+        <v>78762</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772567</v>
+        <v>772628</v>
       </c>
       <c r="R3" t="n">
-        <v>7113274</v>
+        <v>7113321</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122546336</v>
+        <v>122546233</v>
       </c>
       <c r="B4" t="n">
-        <v>91533</v>
+        <v>92213</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,16 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>757</v>
+        <v>4361</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>772541</v>
+        <v>772560</v>
       </c>
       <c r="R4" t="n">
-        <v>7113281</v>
+        <v>7113275</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +967,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122546276</v>
+        <v>122546163</v>
       </c>
       <c r="B5" t="n">
-        <v>78660</v>
+        <v>90940</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,21 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>772628</v>
+        <v>772567</v>
       </c>
       <c r="R5" t="n">
-        <v>7113321</v>
+        <v>7113274</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 49447-2022 artfynd.xlsx
+++ b/artfynd/A 49447-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122546336</v>
       </c>
       <c r="B2" t="n">
-        <v>91636</v>
+        <v>91640</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122546276</v>
+        <v>122546163</v>
       </c>
       <c r="B3" t="n">
-        <v>78762</v>
+        <v>90944</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772628</v>
+        <v>772567</v>
       </c>
       <c r="R3" t="n">
-        <v>7113321</v>
+        <v>7113274</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +886,7 @@
         <v>122546233</v>
       </c>
       <c r="B4" t="n">
-        <v>92213</v>
+        <v>92217</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122546163</v>
+        <v>122546276</v>
       </c>
       <c r="B5" t="n">
-        <v>90940</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,21 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>772567</v>
+        <v>772628</v>
       </c>
       <c r="R5" t="n">
-        <v>7113274</v>
+        <v>7113321</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 49447-2022 artfynd.xlsx
+++ b/artfynd/A 49447-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122546336</v>
+        <v>122546163</v>
       </c>
       <c r="B2" t="n">
-        <v>91640</v>
+        <v>90944</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>757</v>
+        <v>1202</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772541</v>
+        <v>772567</v>
       </c>
       <c r="R2" t="n">
-        <v>7113281</v>
+        <v>7113274</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122546163</v>
+        <v>122546233</v>
       </c>
       <c r="B3" t="n">
-        <v>90944</v>
+        <v>92217</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772567</v>
+        <v>772560</v>
       </c>
       <c r="R3" t="n">
-        <v>7113274</v>
+        <v>7113275</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122546233</v>
+        <v>122546276</v>
       </c>
       <c r="B4" t="n">
-        <v>92217</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>772560</v>
+        <v>772628</v>
       </c>
       <c r="R4" t="n">
-        <v>7113275</v>
+        <v>7113321</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122546276</v>
+        <v>122546336</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>91640</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,21 +1009,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>772628</v>
+        <v>772541</v>
       </c>
       <c r="R5" t="n">
-        <v>7113321</v>
+        <v>7113281</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,6 +1072,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49447-2022 artfynd.xlsx
+++ b/artfynd/A 49447-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122546163</v>
+        <v>122546233</v>
       </c>
       <c r="B2" t="n">
-        <v>90944</v>
+        <v>92217</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772567</v>
+        <v>772560</v>
       </c>
       <c r="R2" t="n">
-        <v>7113274</v>
+        <v>7113275</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122546233</v>
+        <v>122546336</v>
       </c>
       <c r="B3" t="n">
-        <v>92217</v>
+        <v>91640</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Orange taggsvamp</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772560</v>
+        <v>772541</v>
       </c>
       <c r="R3" t="n">
-        <v>7113275</v>
+        <v>7113281</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,6 +860,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -993,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122546336</v>
+        <v>122546163</v>
       </c>
       <c r="B5" t="n">
-        <v>91640</v>
+        <v>90944</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,16 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>757</v>
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>772541</v>
+        <v>772567</v>
       </c>
       <c r="R5" t="n">
-        <v>7113281</v>
+        <v>7113274</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,7 +1073,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49447-2022 artfynd.xlsx
+++ b/artfynd/A 49447-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122546233</v>
+        <v>122546163</v>
       </c>
       <c r="B2" t="n">
-        <v>92217</v>
+        <v>90944</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772560</v>
+        <v>772567</v>
       </c>
       <c r="R2" t="n">
-        <v>7113275</v>
+        <v>7113274</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122546336</v>
+        <v>122546276</v>
       </c>
       <c r="B3" t="n">
-        <v>91640</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,16 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>757</v>
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772541</v>
+        <v>772628</v>
       </c>
       <c r="R3" t="n">
-        <v>7113281</v>
+        <v>7113321</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +865,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -883,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122546276</v>
+        <v>122546233</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>92217</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>772628</v>
+        <v>772560</v>
       </c>
       <c r="R4" t="n">
-        <v>7113321</v>
+        <v>7113275</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122546163</v>
+        <v>122546336</v>
       </c>
       <c r="B5" t="n">
-        <v>90944</v>
+        <v>91640</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,21 +1009,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>772567</v>
+        <v>772541</v>
       </c>
       <c r="R5" t="n">
-        <v>7113274</v>
+        <v>7113281</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,6 +1072,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49447-2022 artfynd.xlsx
+++ b/artfynd/A 49447-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122546163</v>
+        <v>122546336</v>
       </c>
       <c r="B2" t="n">
-        <v>90944</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>757</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772567</v>
+        <v>772541</v>
       </c>
       <c r="R2" t="n">
-        <v>7113274</v>
+        <v>7113281</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +754,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122546276</v>
+        <v>122546163</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772628</v>
+        <v>772567</v>
       </c>
       <c r="R3" t="n">
-        <v>7113321</v>
+        <v>7113274</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,12 +881,7 @@
         <v>122546233</v>
       </c>
       <c r="B4" t="n">
-        <v>92217</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,15 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122546336</v>
+        <v>122546323</v>
       </c>
       <c r="B5" t="n">
-        <v>91640</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,16 +990,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>757</v>
+        <v>4362</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,10 +1014,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>772541</v>
+        <v>772579</v>
       </c>
       <c r="R5" t="n">
-        <v>7113281</v>
+        <v>7113317</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,7 +1058,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1092,6 +1077,705 @@
           <t>Ecogain</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122546324</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rappelmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>772557</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7113312</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122546309</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rappelmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>772572</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7113317</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122546239</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rappelmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>772596</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7113311</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122546275</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rappelmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>772572</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7113319</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122546276</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rappelmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>772628</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7113321</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122549208</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rappelmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>772633</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7113350</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Lussetti</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Lussetti</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122549202</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rappelmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>772642</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7113333</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Lussetti</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Lussetti</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49447-2022 artfynd.xlsx
+++ b/artfynd/A 49447-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122546336</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122546163</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122546233</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122546323</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122546324</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122546309</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,6 +1415,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122546239</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1481,6 +1521,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122546275</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1582,6 +1627,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122546276</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1679,6 +1729,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122549208</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1776,8 +1831,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122549202</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>